--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationloisir/Shared Documents/Prestations Loisirs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="774" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA941E8-9070-4013-AC02-332B88EC6F08}"/>
+  <xr:revisionPtr revIDLastSave="799" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2F14847-9C1F-42C2-AD1D-18AE03FA0B1C}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,6 +373,11 @@
             <v>1.135227272727273</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.1595328282828286</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -441,8 +446,8 @@
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
-          <cell r="F2">
-            <v>0.75734722222222195</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -478,6 +483,11 @@
         <row r="11">
           <cell r="K11">
             <v>2.1221091269841272</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.4796488095238096</v>
           </cell>
         </row>
         <row r="19">
@@ -587,6 +597,11 @@
             <v>0.70511363636363633</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.77386363636363631</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -644,6 +659,11 @@
             <v>1.245138888888889</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.5685515873015874</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -749,6 +769,11 @@
         <row r="11">
           <cell r="K11">
             <v>1.1397222222222223</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.9976587301587303</v>
           </cell>
         </row>
         <row r="19">
@@ -906,6 +931,11 @@
             <v>1.1443308080808079</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.2943308080808078</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -995,17 +1025,22 @@
         </row>
         <row r="9">
           <cell r="K9">
-            <v>0.22005718954248363</v>
+            <v>0.23402777777777775</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-3.8844325609031533E-2</v>
+            <v>-2.4179292929292967E-2</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>4.379456327985734E-2</v>
+            <v>5.8459595959595906E-2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.1973484848484848</v>
           </cell>
         </row>
       </sheetData>
@@ -1050,6 +1085,11 @@
             <v>1.2953804347826088</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.1203804347826087</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1118,8 +1158,8 @@
       </sheetData>
       <sheetData sheetId="11">
         <row r="2">
-          <cell r="F2">
-            <v>1.2248654450685339</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1155,6 +1195,11 @@
         <row r="11">
           <cell r="K11">
             <v>3.6589692987312117</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>2.3256359653978782</v>
           </cell>
         </row>
         <row r="19">
@@ -1261,7 +1306,12 @@
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.4440147762454264</v>
+            <v>0.41693144291209305</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.3502647762454264</v>
           </cell>
         </row>
         <row r="19">
@@ -1363,12 +1413,17 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-0.55687158599484443</v>
+            <v>-0.56475037387363236</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>-0.44929222091547927</v>
+            <v>-0.4571710087942672</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>-0.4571710087942672</v>
           </cell>
         </row>
         <row r="19">
@@ -1439,8 +1494,8 @@
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
-          <cell r="F2">
-            <v>0.38935606060606043</v>
+          <cell r="F2" t="str">
+            <v xml:space="preserve"> </v>
           </cell>
         </row>
         <row r="5">
@@ -1476,6 +1531,11 @@
         <row r="11">
           <cell r="K11">
             <v>1.6128186274509797</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.2353900560224083</v>
           </cell>
         </row>
         <row r="19">
@@ -1585,6 +1645,11 @@
             <v>0.33640873015873018</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.3575396825396826</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -1652,6 +1717,11 @@
             <v>1.4433430207600688</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.8375890525061005</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1757,6 +1827,11 @@
         <row r="11">
           <cell r="K11">
             <v>0.35883838383838396</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.42619949494949505</v>
           </cell>
         </row>
         <row r="19">
@@ -1859,12 +1934,17 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.49416035353535381</v>
+            <v>0.49747474747474774</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.5219381313131316</v>
+            <v>0.52525252525252553</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.64955808080808108</v>
           </cell>
         </row>
         <row r="19">
@@ -1974,6 +2054,11 @@
             <v>2.0402777777777779</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>2.8045634920634921</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2081,6 +2166,11 @@
             <v>1.8676111111111118</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.8810238095238101</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2188,6 +2278,11 @@
             <v>0.40868935358624414</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.201844115491006</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2293,6 +2388,11 @@
         <row r="11">
           <cell r="K11">
             <v>0.2203679653679653</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.18247113997113992</v>
           </cell>
         </row>
         <row r="19">
@@ -2353,6 +2453,11 @@
             <v>1.6562500000000002</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.7986111111111114</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -2452,12 +2557,17 @@
         </row>
         <row r="10">
           <cell r="K10">
-            <v>-3.0303030303031608E-3</v>
+            <v>-0.1599747474747476</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>-7.1969696969698127E-3</v>
+            <v>-0.16414141414141425</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>-0.26681998556998565</v>
           </cell>
         </row>
         <row r="19">
@@ -2499,21 +2609,21 @@
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{754EF1F6-D6CE-4B61-B059-689C5D9CEF25}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{2FD1CE32-ECE7-4893-8BC2-4006C2FCF160}" name="Solde 31/08" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{2E7CEC48-66C0-4270-8819-C5AEB96FCCE1}" name="Janvier" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{2FD1CE32-ECE7-4893-8BC2-4006C2FCF160}" name="Solde 31/08" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{2E7CEC48-66C0-4270-8819-C5AEB96FCCE1}" name="Janvier" dataDxfId="12">
       <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0C9F15EC-B037-4437-BD2B-E7CF27699C3A}" name="Février" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{3C217D23-BDAC-4CD8-940B-C4CA82ECA661}" name="Mars" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{7B9C3F84-98FA-457E-AA2C-37B43CA891DE}" name="Avril" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{E9BBC20F-6E7D-483A-A2C4-C1ACB46104CD}" name="Mai" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{24F62277-DAE6-4829-B809-3E2D477715E4}" name="Juin" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{0670983D-E820-43B1-A435-DE806CC60452}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{0CDE416F-EB10-46CE-846C-6E62D241F509}" name="Août" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{CEF508F5-A8A9-4275-A501-618AF335963E}" name="Septembre" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{5A242AD9-4A28-46D7-9DC6-012058F6C4AC}" name="Octobre" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{039DCC9B-124D-4CDE-8FC1-EABB8CB091DC}" name="Novembre" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{406CB3AB-04B7-47C3-A699-F13C6891C693}" name="Décembre" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{0C9F15EC-B037-4437-BD2B-E7CF27699C3A}" name="Février" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{3C217D23-BDAC-4CD8-940B-C4CA82ECA661}" name="Mars" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{7B9C3F84-98FA-457E-AA2C-37B43CA891DE}" name="Avril" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{E9BBC20F-6E7D-483A-A2C4-C1ACB46104CD}" name="Mai" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{24F62277-DAE6-4829-B809-3E2D477715E4}" name="Juin" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{0670983D-E820-43B1-A435-DE806CC60452}" name="Juillet" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{0CDE416F-EB10-46CE-846C-6E62D241F509}" name="Août" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{CEF508F5-A8A9-4275-A501-618AF335963E}" name="Septembre" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{5A242AD9-4A28-46D7-9DC6-012058F6C4AC}" name="Octobre" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{039DCC9B-124D-4CDE-8FC1-EABB8CB091DC}" name="Novembre" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{406CB3AB-04B7-47C3-A699-F13C6891C693}" name="Décembre" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2527,21 +2637,21 @@
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{404799F8-EF23-44D1-82C6-A022BF0100EC}" name="Agent"/>
-    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{CA1AE1FC-3B06-4FE4-B14C-2062768FF719}" name="Solde 31/08" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{E374D505-F3A4-4A54-B661-7A811C5C6CF0}" name="Janvier" dataDxfId="24">
       <calculatedColumnFormula>[1]ANCART!$K$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9D8E114C-EE46-411F-8DB7-F007D2820209}" name="Février" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{944F841B-7157-43A7-BBF4-EE37DB90304B}" name="Mars" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4291,7 +4401,10 @@
         <f>[1]BECKER!$K$11</f>
         <v>1.135227272727273</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1">
+        <f>[1]BECKER!$K$12</f>
+        <v>1.1595328282828286</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -4301,9 +4414,9 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1" t="str">
         <f>[1]BOUSSIFET!$F$2</f>
-        <v>0.75734722222222195</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C3" s="1">
         <f>[1]BOUSSIFET!$K$5</f>
@@ -4333,7 +4446,10 @@
         <f>[1]BOUSSIFET!$K$11</f>
         <v>2.1221091269841272</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1">
+        <f>[1]BOUSSIFET!$K$12</f>
+        <v>1.4796488095238096</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -4375,7 +4491,10 @@
         <f>[1]DEKLERCK!$K$11</f>
         <v>0.70511363636363633</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1">
+        <f>[1]DEKLERCK!$K$12</f>
+        <v>0.77386363636363631</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -4417,7 +4536,10 @@
         <f>[1]DELFORGE!$K$11</f>
         <v>1.245138888888889</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1">
+        <f>[1]DELFORGE!$K$12</f>
+        <v>1.5685515873015874</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -4459,7 +4581,10 @@
         <f>[1]DEWEZ!$K$11</f>
         <v>1.1397222222222223</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <f>[1]DEWEZ!$K$12</f>
+        <v>0.9976587301587303</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -4501,7 +4626,10 @@
         <f>[1]DUCHENE!$K$11</f>
         <v>1.1443308080808079</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1">
+        <f>[1]DUCHENE!$K$12</f>
+        <v>1.2943308080808078</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -4530,17 +4658,20 @@
       </c>
       <c r="G8" s="1">
         <f>[1]DURUISSEAU!$K$9</f>
-        <v>0.22005718954248363</v>
+        <v>0.23402777777777775</v>
       </c>
       <c r="H8" s="1">
         <f>[1]DURUISSEAU!$K$10</f>
-        <v>-3.8844325609031533E-2</v>
+        <v>-2.4179292929292967E-2</v>
       </c>
       <c r="I8" s="1">
         <f>[1]DURUISSEAU!$K$11</f>
-        <v>4.379456327985734E-2</v>
-      </c>
-      <c r="J8" s="1"/>
+        <v>5.8459595959595906E-2</v>
+      </c>
+      <c r="J8" s="1">
+        <f>[1]DURUISSEAU!$K$12</f>
+        <v>0.1973484848484848</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -4582,7 +4713,10 @@
         <f>[1]HEIRBRANT!$K$11</f>
         <v>1.2953804347826088</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <f>[1]HEIRBRANT!$K$12</f>
+        <v>1.1203804347826087</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -4592,9 +4726,9 @@
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="1" t="str">
         <f>[1]INZERILLI!$F$2</f>
-        <v>1.2248654450685339</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C10" s="1">
         <f>[1]INZERILLI!$K$5</f>
@@ -4624,7 +4758,10 @@
         <f>[1]INZERILLI!$K$11</f>
         <v>3.6589692987312117</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="1">
+        <f>[1]INZERILLI!$K$12</f>
+        <v>2.3256359653978782</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -4664,9 +4801,12 @@
       </c>
       <c r="I11" s="1">
         <f>[1]JAMAR!$K$11</f>
-        <v>0.4440147762454264</v>
-      </c>
-      <c r="J11" s="1"/>
+        <v>0.41693144291209305</v>
+      </c>
+      <c r="J11" s="1">
+        <f>[1]JAMAR!$K$12</f>
+        <v>0.3502647762454264</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -4702,13 +4842,16 @@
       </c>
       <c r="H12" s="1">
         <f>[1]JAMART!$K$10</f>
-        <v>-0.55687158599484443</v>
+        <v>-0.56475037387363236</v>
       </c>
       <c r="I12" s="1">
         <f>[1]JAMART!$K$11</f>
-        <v>-0.44929222091547927</v>
-      </c>
-      <c r="J12" s="1"/>
+        <v>-0.4571710087942672</v>
+      </c>
+      <c r="J12" s="1">
+        <f>[1]JAMART!$K$12</f>
+        <v>-0.4571710087942672</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -4718,9 +4861,9 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="1" t="str">
         <f>[1]KINIF!$F$2</f>
-        <v>0.38935606060606043</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C13" s="1">
         <f>[1]KINIF!$K$5</f>
@@ -4750,7 +4893,10 @@
         <f>[1]KINIF!$K$11</f>
         <v>1.6128186274509797</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1">
+        <f>[1]KINIF!$K$12</f>
+        <v>1.2353900560224083</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -4792,7 +4938,10 @@
         <f>[1]LABBE!$K$11</f>
         <v>0.33640873015873018</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1">
+        <f>[1]LABBE!$K$12</f>
+        <v>0.3575396825396826</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -4834,7 +4983,10 @@
         <f>[1]LAMBERT!$K$11</f>
         <v>1.4433430207600688</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1">
+        <f>[1]LAMBERT!$K$12</f>
+        <v>0.8375890525061005</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -4876,7 +5028,10 @@
         <f>[1]LEMAITRE!$K$11</f>
         <v>0.35883838383838396</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1">
+        <f>[1]LEMAITRE!$K$12</f>
+        <v>0.42619949494949505</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -4912,13 +5067,16 @@
       </c>
       <c r="H17" s="1">
         <f>[1]LIEGEOIS!$K$10</f>
-        <v>0.49416035353535381</v>
+        <v>0.49747474747474774</v>
       </c>
       <c r="I17" s="1">
         <f>[1]LIEGEOIS!$K$11</f>
-        <v>0.5219381313131316</v>
-      </c>
-      <c r="J17" s="1"/>
+        <v>0.52525252525252553</v>
+      </c>
+      <c r="J17" s="1">
+        <f>[1]LIEGEOIS!$K$12</f>
+        <v>0.64955808080808108</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -4960,7 +5118,10 @@
         <f>[1]MOSCATO!$K$11</f>
         <v>2.0402777777777779</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1">
+        <f>[1]MOSCATO!$K$12</f>
+        <v>2.8045634920634921</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -5002,7 +5163,10 @@
         <f>[1]NEZER!$K$11</f>
         <v>1.8676111111111118</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1">
+        <f>[1]NEZER!$K$12</f>
+        <v>1.8810238095238101</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -5044,7 +5208,10 @@
         <f>[1]PESESSE!$K$11</f>
         <v>0.40868935358624414</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1">
+        <f>[1]PESESSE!$K$12</f>
+        <v>1.201844115491006</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -5086,7 +5253,10 @@
         <f>[1]SEGHIAR!$K$11</f>
         <v>0.2203679653679653</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1">
+        <f>[1]SEGHIAR!$K$12</f>
+        <v>0.18247113997113992</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -5128,7 +5298,10 @@
         <f>[1]SUSAM!$K$11</f>
         <v>1.6562500000000002</v>
       </c>
-      <c r="J22" s="1"/>
+      <c r="J22" s="1">
+        <f>[1]SUSAM!$K$12</f>
+        <v>1.7986111111111114</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -5164,13 +5337,16 @@
       </c>
       <c r="H23" s="1">
         <f>[1]TIBEAU!$K$10</f>
-        <v>-3.0303030303031608E-3</v>
+        <v>-0.1599747474747476</v>
       </c>
       <c r="I23" s="1">
         <f>[1]TIBEAU!$K$11</f>
-        <v>-7.1969696969698127E-3</v>
-      </c>
-      <c r="J23" s="1"/>
+        <v>-0.16414141414141425</v>
+      </c>
+      <c r="J23" s="1">
+        <f>[1]TIBEAU!$K$12</f>
+        <v>-0.26681998556998565</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -5189,25 +5365,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a6b1418315c503125b81deceb3e14f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db3d71b0-92fa-400b-b303-110676c7e1a6" xmlns:ns3="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b9cfce4172cb86f233e713e45f29f51c" ns2:_="" ns3:_="">
     <xsd:import namespace="db3d71b0-92fa-400b-b303-110676c7e1a6"/>
@@ -5418,25 +5575,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A27A95-3717-46C0-8F53-2FF09BECAD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5453,4 +5611,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{1456b5d2-d0ee-4225-910f-b53e3f31b6d6}" enabled="0" method="" siteId="{1456b5d2-d0ee-4225-910f-b53e3f31b6d6}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/data/HeureLoisir.xlsx
+++ b/data/HeureLoisir.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationloisir/Shared Documents/Prestations Loisirs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="799" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2F14847-9C1F-42C2-AD1D-18AE03FA0B1C}"/>
+  <xr:revisionPtr revIDLastSave="803" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D67E5F70-DBAA-4907-8A4A-C79C9825C894}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -350,32 +350,37 @@
         </row>
         <row r="7">
           <cell r="K7">
-            <v>2.3296717171717174</v>
+            <v>2.5359217171717177</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>2.0859217171717175</v>
+            <v>2.2921717171717177</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>1.4623106060606064</v>
+            <v>1.6685606060606066</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>1.2900883838383841</v>
+            <v>1.4963383838383844</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>1.135227272727273</v>
+            <v>1.3414772727272732</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1.1595328282828286</v>
+            <v>1.3657828282828288</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.83522727272727326</v>
           </cell>
         </row>
         <row r="19">
@@ -490,6 +495,11 @@
             <v>1.4796488095238096</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.4206210317460317</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -602,6 +612,11 @@
             <v>0.77386363636363631</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.67998737373737361</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -664,6 +679,11 @@
             <v>1.5685515873015874</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.5650793650793653</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -776,6 +796,11 @@
             <v>0.9976587301587303</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.0122420634920637</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -822,7 +847,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="19">
           <cell r="E19" t="str">
@@ -936,6 +961,11 @@
             <v>1.2943308080808078</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1700252525252521</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1043,6 +1073,11 @@
             <v>0.1973484848484848</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>7.4053030303030259E-2</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="2">
@@ -1090,6 +1125,11 @@
             <v>1.1203804347826087</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.84815821256038648</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1202,6 +1242,11 @@
             <v>2.3256359653978782</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>2.2966586926706056</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1314,6 +1359,11 @@
             <v>0.3502647762454264</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.42080770553835573</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1426,6 +1476,11 @@
             <v>-0.4571710087942672</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>-0.27535282697608537</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1538,6 +1593,11 @@
             <v>1.2353900560224083</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.227056722689075</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1650,6 +1710,11 @@
             <v>0.3575396825396826</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.19402958152958161</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -1719,7 +1784,12 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0.8375890525061005</v>
+            <v>0.86139857631562433</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.62648696015400818</v>
           </cell>
         </row>
         <row r="19">
@@ -1834,6 +1904,11 @@
             <v>0.42619949494949505</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.29981060606060617</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1900,7 +1975,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="18"/>
       <sheetData sheetId="19">
         <row r="2">
           <cell r="F2" t="str">
@@ -1945,6 +2020,11 @@
         <row r="12">
           <cell r="K12">
             <v>0.64955808080808108</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.74930555555555589</v>
           </cell>
         </row>
         <row r="19">
@@ -2056,7 +2136,12 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2.8045634920634921</v>
+            <v>2.8277777777777779</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>2.4839646464646465</v>
           </cell>
         </row>
         <row r="19">
@@ -2163,12 +2248,17 @@
         </row>
         <row r="11">
           <cell r="K11">
-            <v>1.8676111111111118</v>
+            <v>1.9127500000000006</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1.8810238095238101</v>
+            <v>1.9261626984126989</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.8094960317460322</v>
           </cell>
         </row>
         <row r="19">
@@ -2265,22 +2355,27 @@
         </row>
         <row r="9">
           <cell r="K9">
-            <v>0.28481669846358904</v>
+            <v>0.52355852852894846</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>0.35779649644338701</v>
+            <v>0.59642469014511001</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.40868935358624414</v>
+            <v>0.64719849966891951</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1.201844115491006</v>
+            <v>1.5966032615736814</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.5827269989474186</v>
           </cell>
         </row>
         <row r="19">
@@ -2395,6 +2490,11 @@
             <v>0.18247113997113992</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>7.3127705627705569E-2</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0</v>
@@ -2411,7 +2511,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="24"/>
       <sheetData sheetId="25">
         <row r="2">
           <cell r="F2" t="str">
@@ -2456,6 +2556,11 @@
         <row r="12">
           <cell r="K12">
             <v>1.7986111111111114</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>2.0284722222222227</v>
           </cell>
         </row>
         <row r="19">
@@ -2568,6 +2673,11 @@
         <row r="12">
           <cell r="K12">
             <v>-0.26681998556998565</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>-0.4466179653679655</v>
           </cell>
         </row>
         <row r="19">
@@ -2647,8 +2757,8 @@
     <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
     <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
     <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
     <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="14"/>
@@ -4383,29 +4493,32 @@
       </c>
       <c r="E2" s="1">
         <f>[1]BECKER!$K$7</f>
-        <v>2.3296717171717174</v>
+        <v>2.5359217171717177</v>
       </c>
       <c r="F2" s="1">
         <f>[1]BECKER!$K$8</f>
-        <v>2.0859217171717175</v>
+        <v>2.2921717171717177</v>
       </c>
       <c r="G2" s="1">
         <f>[1]BECKER!$K$9</f>
-        <v>1.4623106060606064</v>
+        <v>1.6685606060606066</v>
       </c>
       <c r="H2" s="1">
         <f>[1]BECKER!$K$10</f>
-        <v>1.2900883838383841</v>
+        <v>1.4963383838383844</v>
       </c>
       <c r="I2" s="1">
         <f>[1]BECKER!$K$11</f>
-        <v>1.135227272727273</v>
+        <v>1.3414772727272732</v>
       </c>
       <c r="J2" s="1">
         <f>[1]BECKER!$K$12</f>
-        <v>1.1595328282828286</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>1.3657828282828288</v>
+      </c>
+      <c r="K2" s="1">
+        <f>[1]BECKER!$K$13</f>
+        <v>0.83522727272727326</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -4450,7 +4563,10 @@
         <f>[1]BOUSSIFET!$K$12</f>
         <v>1.4796488095238096</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1">
+        <f>[1]BOUSSIFET!$K$13</f>
+        <v>1.4206210317460317</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -4495,7 +4611,10 @@
         <f>[1]DEKLERCK!$K$12</f>
         <v>0.77386363636363631</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1">
+        <f>[1]DEKLERCK!$K$13</f>
+        <v>0.67998737373737361</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -4540,7 +4659,10 @@
         <f>[1]DELFORGE!$K$12</f>
         <v>1.5685515873015874</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1">
+        <f>[1]DELFORGE!$K$13</f>
+        <v>1.5650793650793653</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -4585,7 +4707,10 @@
         <f>[1]DEWEZ!$K$12</f>
         <v>0.9976587301587303</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <f>[1]DEWEZ!$K$13</f>
+        <v>1.0122420634920637</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -4630,7 +4755,10 @@
         <f>[1]DUCHENE!$K$12</f>
         <v>1.2943308080808078</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <f>[1]DUCHENE!$K$13</f>
+        <v>1.1700252525252521</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -4672,7 +4800,10 @@
         <f>[1]DURUISSEAU!$K$12</f>
         <v>0.1973484848484848</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <f>[1]DURUISSEAU!$K$13</f>
+        <v>7.4053030303030259E-2</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -4717,7 +4848,10 @@
         <f>[1]HEIRBRANT!$K$12</f>
         <v>1.1203804347826087</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <f>[1]HEIRBRANT!$K$13</f>
+        <v>0.84815821256038648</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -4762,7 +4896,10 @@
         <f>[1]INZERILLI!$K$12</f>
         <v>2.3256359653978782</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <f>[1]INZERILLI!$K$13</f>
+        <v>2.2966586926706056</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -4807,7 +4944,10 @@
         <f>[1]JAMAR!$K$12</f>
         <v>0.3502647762454264</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <f>[1]JAMAR!$K$13</f>
+        <v>0.42080770553835573</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -4852,7 +4992,10 @@
         <f>[1]JAMART!$K$12</f>
         <v>-0.4571710087942672</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <f>[1]JAMART!$K$13</f>
+        <v>-0.27535282697608537</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4897,7 +5040,10 @@
         <f>[1]KINIF!$K$12</f>
         <v>1.2353900560224083</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <f>[1]KINIF!$K$13</f>
+        <v>1.227056722689075</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -4942,7 +5088,10 @@
         <f>[1]LABBE!$K$12</f>
         <v>0.3575396825396826</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1">
+        <f>[1]LABBE!$K$13</f>
+        <v>0.19402958152958161</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -4985,9 +5134,12 @@
       </c>
       <c r="J15" s="1">
         <f>[1]LAMBERT!$K$12</f>
-        <v>0.8375890525061005</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>0.86139857631562433</v>
+      </c>
+      <c r="K15" s="1">
+        <f>[1]LAMBERT!$K$13</f>
+        <v>0.62648696015400818</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -5032,7 +5184,10 @@
         <f>[1]LEMAITRE!$K$12</f>
         <v>0.42619949494949505</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1">
+        <f>[1]LEMAITRE!$K$13</f>
+        <v>0.29981060606060617</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -5077,7 +5232,10 @@
         <f>[1]LIEGEOIS!$K$12</f>
         <v>0.64955808080808108</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <f>[1]LIEGEOIS!$K$13</f>
+        <v>0.74930555555555589</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -5120,9 +5278,12 @@
       </c>
       <c r="J18" s="1">
         <f>[1]MOSCATO!$K$12</f>
-        <v>2.8045634920634921</v>
-      </c>
-      <c r="K18" s="1"/>
+        <v>2.8277777777777779</v>
+      </c>
+      <c r="K18" s="1">
+        <f>[1]MOSCATO!$K$13</f>
+        <v>2.4839646464646465</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -5161,13 +5322,16 @@
       </c>
       <c r="I19" s="1">
         <f>[1]NEZER!$K$11</f>
-        <v>1.8676111111111118</v>
+        <v>1.9127500000000006</v>
       </c>
       <c r="J19" s="1">
         <f>[1]NEZER!$K$12</f>
-        <v>1.8810238095238101</v>
-      </c>
-      <c r="K19" s="1"/>
+        <v>1.9261626984126989</v>
+      </c>
+      <c r="K19" s="1">
+        <f>[1]NEZER!$K$13</f>
+        <v>1.8094960317460322</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -5198,21 +5362,24 @@
       </c>
       <c r="G20" s="1">
         <f>[1]PESESSE!$K$9</f>
-        <v>0.28481669846358904</v>
+        <v>0.52355852852894846</v>
       </c>
       <c r="H20" s="1">
         <f>[1]PESESSE!$K$10</f>
-        <v>0.35779649644338701</v>
+        <v>0.59642469014511001</v>
       </c>
       <c r="I20" s="1">
         <f>[1]PESESSE!$K$11</f>
-        <v>0.40868935358624414</v>
+        <v>0.64719849966891951</v>
       </c>
       <c r="J20" s="1">
         <f>[1]PESESSE!$K$12</f>
-        <v>1.201844115491006</v>
-      </c>
-      <c r="K20" s="1"/>
+        <v>1.5966032615736814</v>
+      </c>
+      <c r="K20" s="1">
+        <f>[1]PESESSE!$K$13</f>
+        <v>1.5827269989474186</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -5257,7 +5424,10 @@
         <f>[1]SEGHIAR!$K$12</f>
         <v>0.18247113997113992</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1">
+        <f>[1]SEGHIAR!$K$13</f>
+        <v>7.3127705627705569E-2</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -5302,7 +5472,10 @@
         <f>[1]SUSAM!$K$12</f>
         <v>1.7986111111111114</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1">
+        <f>[1]SUSAM!$K$13</f>
+        <v>2.0284722222222227</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -5347,7 +5520,10 @@
         <f>[1]TIBEAU!$K$12</f>
         <v>-0.26681998556998565</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1">
+        <f>[1]TIBEAU!$K$13</f>
+        <v>-0.4466179653679655</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -5365,6 +5541,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a6b1418315c503125b81deceb3e14f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db3d71b0-92fa-400b-b303-110676c7e1a6" xmlns:ns3="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b9cfce4172cb86f233e713e45f29f51c" ns2:_="" ns3:_="">
     <xsd:import namespace="db3d71b0-92fa-400b-b303-110676c7e1a6"/>
@@ -5575,16 +5761,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d07ca0ec-5157-41b5-8d0f-93bd9610df36">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5595,6 +5771,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A27A95-3717-46C0-8F53-2FF09BECAD9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5613,16 +5799,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
   <ds:schemaRefs>
